--- a/plm python control/wrappers/multibeam parameters/multibeam 9 spot sequence/multiBeam_9_spot_25_BeamA_080_BeamB_100.xlsx
+++ b/plm python control/wrappers/multibeam parameters/multibeam 9 spot sequence/multiBeam_9_spot_25_BeamA_080_BeamB_100.xlsx
@@ -442,7 +442,7 @@
         <v>5</v>
       </c>
       <c r="D6">
-        <v>43.4</v>
+        <v>41.4</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -512,7 +512,7 @@
         <v>8</v>
       </c>
       <c r="D11">
-        <v>1.501681768714213</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -582,7 +582,7 @@
         <v>5</v>
       </c>
       <c r="D17">
-        <v>47.8</v>
+        <v>45.8</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -722,7 +722,7 @@
         <v>5</v>
       </c>
       <c r="D28">
-        <v>48.4</v>
+        <v>46.4</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -862,7 +862,7 @@
         <v>5</v>
       </c>
       <c r="D39">
-        <v>46.4</v>
+        <v>44.4</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -932,7 +932,7 @@
         <v>8</v>
       </c>
       <c r="D44">
-        <v>1.4</v>
+        <v>1.076901077801928</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -1002,7 +1002,7 @@
         <v>5</v>
       </c>
       <c r="D50">
-        <v>50.2</v>
+        <v>48.2</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -1142,7 +1142,7 @@
         <v>5</v>
       </c>
       <c r="D61">
-        <v>52.2</v>
+        <v>50.2</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -1282,7 +1282,7 @@
         <v>5</v>
       </c>
       <c r="D72">
-        <v>52.2</v>
+        <v>50.2</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -1352,7 +1352,7 @@
         <v>8</v>
       </c>
       <c r="D77">
-        <v>1.4</v>
+        <v>1.404820383850808</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -1422,7 +1422,7 @@
         <v>5</v>
       </c>
       <c r="D83">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -1562,7 +1562,7 @@
         <v>5</v>
       </c>
       <c r="D94">
-        <v>42.2</v>
+        <v>40.2</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -1702,7 +1702,7 @@
         <v>5</v>
       </c>
       <c r="D105">
-        <v>46.6</v>
+        <v>44.6</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -1842,7 +1842,7 @@
         <v>5</v>
       </c>
       <c r="D116">
-        <v>47.2</v>
+        <v>45.2</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -1982,7 +1982,7 @@
         <v>5</v>
       </c>
       <c r="D127">
-        <v>46.6</v>
+        <v>44.6</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -2122,7 +2122,7 @@
         <v>5</v>
       </c>
       <c r="D138">
-        <v>52.8</v>
+        <v>50.8</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -2262,7 +2262,7 @@
         <v>5</v>
       </c>
       <c r="D149">
-        <v>56.4</v>
+        <v>54.4</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -2402,7 +2402,7 @@
         <v>5</v>
       </c>
       <c r="D160">
-        <v>46.6</v>
+        <v>44.6</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -2542,7 +2542,7 @@
         <v>5</v>
       </c>
       <c r="D171">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -2682,7 +2682,7 @@
         <v>5</v>
       </c>
       <c r="D182">
-        <v>42.2</v>
+        <v>40.2</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -2822,7 +2822,7 @@
         <v>5</v>
       </c>
       <c r="D193">
-        <v>42.8</v>
+        <v>40.8</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -2962,7 +2962,7 @@
         <v>5</v>
       </c>
       <c r="D204">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -3102,7 +3102,7 @@
         <v>5</v>
       </c>
       <c r="D215">
-        <v>44.6</v>
+        <v>42.6</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -3242,7 +3242,7 @@
         <v>5</v>
       </c>
       <c r="D226">
-        <v>52.8</v>
+        <v>50.8</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -3382,7 +3382,7 @@
         <v>5</v>
       </c>
       <c r="D237">
-        <v>36.4</v>
+        <v>34.4</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -3522,7 +3522,7 @@
         <v>5</v>
       </c>
       <c r="D248">
-        <v>42.2</v>
+        <v>40.2</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -3662,7 +3662,7 @@
         <v>5</v>
       </c>
       <c r="D259">
-        <v>37.2</v>
+        <v>35.2</v>
       </c>
     </row>
     <row r="260" spans="1:4">
@@ -3802,7 +3802,7 @@
         <v>5</v>
       </c>
       <c r="D270">
-        <v>40.8</v>
+        <v>38.8</v>
       </c>
     </row>
     <row r="271" spans="1:4">
@@ -3872,7 +3872,7 @@
         <v>8</v>
       </c>
       <c r="D275">
-        <v>1.2</v>
+        <v>1.05</v>
       </c>
     </row>
     <row r="277" spans="1:4">
@@ -3942,7 +3942,7 @@
         <v>5</v>
       </c>
       <c r="D281">
-        <v>42.8</v>
+        <v>40.8</v>
       </c>
     </row>
     <row r="282" spans="1:4">
@@ -4082,7 +4082,7 @@
         <v>5</v>
       </c>
       <c r="D292">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="293" spans="1:4">
@@ -4222,7 +4222,7 @@
         <v>5</v>
       </c>
       <c r="D303">
-        <v>51.4</v>
+        <v>49.4</v>
       </c>
     </row>
     <row r="304" spans="1:4">
@@ -4292,7 +4292,7 @@
         <v>8</v>
       </c>
       <c r="D308">
-        <v>1.2</v>
+        <v>1.076962886884533</v>
       </c>
     </row>
     <row r="310" spans="1:4">
@@ -4362,7 +4362,7 @@
         <v>5</v>
       </c>
       <c r="D314">
-        <v>38.4</v>
+        <v>36.4</v>
       </c>
     </row>
     <row r="315" spans="1:4">
@@ -4502,7 +4502,7 @@
         <v>5</v>
       </c>
       <c r="D325">
-        <v>42.2</v>
+        <v>40.2</v>
       </c>
     </row>
     <row r="326" spans="1:4">
@@ -4642,7 +4642,7 @@
         <v>5</v>
       </c>
       <c r="D336">
-        <v>38.4</v>
+        <v>36.4</v>
       </c>
     </row>
     <row r="337" spans="1:4">
@@ -4782,7 +4782,7 @@
         <v>5</v>
       </c>
       <c r="D347">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="348" spans="1:4">
@@ -4922,7 +4922,7 @@
         <v>5</v>
       </c>
       <c r="D358">
-        <v>41.4</v>
+        <v>39.4</v>
       </c>
     </row>
     <row r="359" spans="1:4">
@@ -5062,7 +5062,7 @@
         <v>5</v>
       </c>
       <c r="D369">
-        <v>39.6</v>
+        <v>37.6</v>
       </c>
     </row>
     <row r="370" spans="1:4">
@@ -5202,7 +5202,7 @@
         <v>5</v>
       </c>
       <c r="D380">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="381" spans="1:4">
@@ -5342,7 +5342,7 @@
         <v>5</v>
       </c>
       <c r="D391">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="392" spans="1:4">
@@ -5482,7 +5482,7 @@
         <v>5</v>
       </c>
       <c r="D402">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="403" spans="1:4">
@@ -5622,7 +5622,7 @@
         <v>5</v>
       </c>
       <c r="D413">
-        <v>42.2</v>
+        <v>40.2</v>
       </c>
     </row>
     <row r="414" spans="1:4">
@@ -5762,7 +5762,7 @@
         <v>5</v>
       </c>
       <c r="D424">
-        <v>37.8</v>
+        <v>35.8</v>
       </c>
     </row>
     <row r="425" spans="1:4">
@@ -5902,7 +5902,7 @@
         <v>5</v>
       </c>
       <c r="D435">
-        <v>37.2</v>
+        <v>35.2</v>
       </c>
     </row>
     <row r="436" spans="1:4">
@@ -6042,7 +6042,7 @@
         <v>5</v>
       </c>
       <c r="D446">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="447" spans="1:4">
@@ -6182,7 +6182,7 @@
         <v>5</v>
       </c>
       <c r="D457">
-        <v>37.8</v>
+        <v>35.8</v>
       </c>
     </row>
     <row r="458" spans="1:4">
@@ -6322,7 +6322,7 @@
         <v>5</v>
       </c>
       <c r="D468">
-        <v>29.6</v>
+        <v>27.6</v>
       </c>
     </row>
     <row r="469" spans="1:4">
@@ -6392,7 +6392,7 @@
         <v>8</v>
       </c>
       <c r="D473">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="475" spans="1:4">
@@ -6462,7 +6462,7 @@
         <v>5</v>
       </c>
       <c r="D479">
-        <v>35.8</v>
+        <v>33.8</v>
       </c>
     </row>
     <row r="480" spans="1:4">
@@ -6602,7 +6602,7 @@
         <v>5</v>
       </c>
       <c r="D490">
-        <v>34.6</v>
+        <v>32.6</v>
       </c>
     </row>
     <row r="491" spans="1:4">
@@ -6742,7 +6742,7 @@
         <v>5</v>
       </c>
       <c r="D501">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="502" spans="1:4">
@@ -6882,7 +6882,7 @@
         <v>5</v>
       </c>
       <c r="D512">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="513" spans="1:4">
@@ -7022,7 +7022,7 @@
         <v>5</v>
       </c>
       <c r="D523">
-        <v>41.4</v>
+        <v>39.4</v>
       </c>
     </row>
     <row r="524" spans="1:4">
@@ -7162,7 +7162,7 @@
         <v>5</v>
       </c>
       <c r="D534">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="535" spans="1:4">
@@ -7232,7 +7232,7 @@
         <v>8</v>
       </c>
       <c r="D539">
-        <v>1.85</v>
+        <v>1.632225821237365</v>
       </c>
     </row>
   </sheetData>
